--- a/Design/Excel/ET/Datas/Product/DishConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/DishConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1173,6 +1173,11 @@
           <t>FinalStageId</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RequiresOrderBinding</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1205,6 +1210,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1237,6 +1247,11 @@
           <t>FinalStageId</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RequiresOrderBinding</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1269,6 +1284,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1299,6 +1319,48 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>鲜榨橙汁</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
